--- a/public/templates/000_pm_suite/02_프로젝트 개발/03_분석/01_요구사항협의/프로젝트명_요구사항질의서_V1.0_20230530.xlsx
+++ b/public/templates/000_pm_suite/02_프로젝트 개발/03_분석/01_요구사항협의/프로젝트명_요구사항질의서_V1.0_20230530.xlsx
@@ -518,14 +518,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[PM-33] 한빛글로벌 SyncGuard AI 현업 인터뷰 요구사항 상세 질의서 — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[PM-33] 한빛글로벌 SyncFlow AI 현업 인터뷰 요구사항 상세 질의서 — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>규제심의팀·마케팅팀·IT정보화팀 심층 인터뷰(3회차) 질의 및 설계 확정 내역 | 발주처: 주식회사 한빛글로벌 | 수행사: 주식회사 엠파시 | 기준일: 2026.10</t>
+          <t>규제검증팀·구매조달팀·IT정보화팀 심층 인터뷰(3회차) 질의 및 설계 확정 내역 | 발주처: 주식회사 한빛글로벌 | 수행사: 주식회사 엠파시 | 기준일: 2026.10</t>
         </is>
       </c>
     </row>
@@ -574,22 +574,22 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>규제심의팀</t>
+          <t>규제검증팀</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>심의 판정 등급</t>
+          <t>검증 판정 등급</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>AI 심의 결과의 판정 단계는 몇 단계로 구분하며 각 기준은 무엇입니까?</t>
+          <t>AI 검증 결과의 판정 단계는 몇 단계로 구분하며 각 기준은 무엇입니까?</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>적격(PASS, 녹색), 주의·실증자료 확인필요(WARN, 황색), 법령위반 금지(FAIL, 적색) 3단계 신호등 체계로 구분함.</t>
+          <t>적격(PASS, 녹색), 주의·시험성적서 확인필요(WARN, 황색), 법령위반 금지(FAIL, 적색) 3단계 신호등 체계로 구분함.</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -611,22 +611,22 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>규제심의팀</t>
+          <t>규제검증팀</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>실증자료 매핑</t>
+          <t>시험성적서 매핑</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>'피부 장벽 72시간 보습 지속' 등 인체적용시험 실증 대상 문구는 어떻게 처리합니까?</t>
+          <t>'절연 내력 2,000시간 내열·진동 보증' 등 공인신뢰성시험 시험검증 대상 조항은 어떻게 처리합니까?</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>2단계 RAG가 실증 키워드를 검출하면 '주의(WARN)'로 분류하고 인체적용시험 보고서 번호 입력란을 활성화함.</t>
+          <t>2단계 RAG가 시험검증 키워드를 검출하면 '주의(WARN)'로 분류하고 공인신뢰성시험 보고서 번호 입력란을 활성화함.</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -648,22 +648,22 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>럭셔리마케팅팀</t>
+          <t>핵심모듈구매조달팀</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>대체문구 추천</t>
+          <t>표준수정조항 추천</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>위반 문구 적발 시 마케터가 즉시 수정할 수 있도록 대체 카피를 몇 개 제안합니까?</t>
+          <t>위반 조항 적발 시 구매담당자가 즉시 수정할 수 있도록 대체 조항를 몇 개 제안합니까?</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>브랜드 톤앤매너를 유지하면서 식약처 가이드라인을 준수하는 안전 대체 표현 3가지를 AI가 즉시 제시함.</t>
+          <t>사업본부 톤앤매너를 유지하면서 공정위·표준원 가이드라인을 준수하는 안전 대체 표현 3가지를 AI가 즉시 제시함.</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -685,22 +685,22 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>더마화장품팀</t>
+          <t>정밀전장전장부품팀</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>전성분 한도 대조</t>
+          <t>자재BOM 한도 대조</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>살리실산(0.5% 한도) 등 사용한도 원료가 홍보문안에 강조된 경우 어떻게 검증합니까?</t>
+          <t>살리실산(0.5% 한도) 등 사용한도 원소재가 조달계약조항에 강조된 경우 어떻게 검증합니까?</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>ProductLab 전성분 뷰의 실제 배합비(%)와 식약처 고시 한도를 대조하여 초과 또는 미함유 시 즉시 적색 경고를 표시함.</t>
+          <t>PLM-Nexus 자재BOM 뷰의 실제 조성비(%)와 공정위·표준원 고시 한도를 대조하여 초과 또는 미함유 시 즉시 적색 경고를 표시함.</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>심의 요청 원문, AI 판정 결과, 심의관 최종 승인 이력의 법적 보관 주기는?</t>
+          <t>검증 요청 원문, AI 판정 결과, 검토위원 최종 승인 이력의 법적 보관 주기는?</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>표시·광고 실증자료 제출 명령에 대비하여 최소 5년간 월별 파티션 테이블 및 S3 아카이브에 불변 보관함.</t>
+          <t>계약·기술규격 시험성적서 제출 명령에 대비하여 최소 5년간 월별 파티션 테이블 및 S3 아카이브에 불변 보관함.</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
